--- a/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_39.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_39.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2253719.236885475</v>
+        <v>2246786.835085624</v>
       </c>
     </row>
     <row r="7">
@@ -748,13 +748,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>135.3518862151736</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -781,13 +781,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
-        <v>147.2737972923793</v>
+        <v>385</v>
       </c>
       <c r="S3" t="n">
         <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
-        <v>5.357765217513816</v>
+        <v>385</v>
       </c>
       <c r="U3" t="n">
         <v>0.2103597601867477</v>
@@ -796,7 +796,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>32.37314290982852</v>
+        <v>99.651064712665</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -845,7 +845,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>119.040440756494</v>
+        <v>120.6316114025499</v>
       </c>
       <c r="N4" t="n">
         <v>171.1850752716849</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573350953</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>94.84816780232291</v>
+        <v>123.5543591877376</v>
       </c>
       <c r="T5" t="n">
         <v>186.6755817285639</v>
@@ -973,13 +973,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
@@ -1024,7 +1024,7 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T6" t="n">
-        <v>385</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
         <v>0.2103597601867477</v>
@@ -1039,7 +1039,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>305.0041245104572</v>
+        <v>153.9536147159908</v>
       </c>
     </row>
     <row r="7">
@@ -1146,10 +1146,10 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
-        <v>36.71585008894188</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1216,10 +1216,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>314.8597026170469</v>
       </c>
       <c r="F9" t="n">
-        <v>121.1806207102953</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>325.7395358750273</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,10 +1252,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>385</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
         <v>66.5639999646113</v>
@@ -1386,7 +1386,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T11" t="n">
         <v>236.6755817285639</v>
@@ -1684,7 +1684,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>75.83998807325922</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D15" t="n">
         <v>347.9376868977026</v>
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>64.74007562773993</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1857,10 +1857,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H17" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>73.04152018756567</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U18" t="n">
-        <v>50.21035976018675</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V18" t="n">
         <v>64.51066719152016</v>
@@ -1984,7 +1984,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X18" t="n">
-        <v>69.86273944538755</v>
+        <v>132.54050197083</v>
       </c>
       <c r="Y18" t="n">
         <v>49.39139276613435</v>
@@ -2088,7 +2088,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F20" t="n">
-        <v>54.88962870801186</v>
+        <v>58.85502009342638</v>
       </c>
       <c r="G20" t="n">
         <v>53.75737228701621</v>
@@ -2097,7 +2097,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I20" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2161,10 +2161,10 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>70.00566530352997</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2218,10 +2218,10 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>145.050905435271</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X21" t="n">
-        <v>419.8627394453875</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y21" t="n">
         <v>49.39139276613435</v>
@@ -2331,10 +2331,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H23" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I23" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2395,16 +2395,16 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>11.09991244551929</v>
+        <v>81.10557774904923</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>73.04152018756569</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2598,10 +2598,10 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>7.224591385414723</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>192.8481678023229</v>
+        <v>200.0727591877375</v>
       </c>
       <c r="T26" t="n">
         <v>284.6755817285639</v>
@@ -2738,22 +2738,22 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>119.9109885154183</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>269.1850752716849</v>
       </c>
       <c r="O28" t="n">
-        <v>303.7023614405202</v>
+        <v>338.445564079015</v>
       </c>
       <c r="P28" t="n">
         <v>385.4478973282775</v>
       </c>
       <c r="Q28" t="n">
-        <v>423.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2808,7 +2808,7 @@
         <v>106.0096587035274</v>
       </c>
       <c r="I29" t="n">
-        <v>7.224591385414625</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2838,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>192.8481678023229</v>
+        <v>200.0727591877375</v>
       </c>
       <c r="T29" t="n">
         <v>284.6755817285639</v>
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>121.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>218.6316114025499</v>
+        <v>119.9109885154183</v>
       </c>
       <c r="N31" t="n">
         <v>269.1850752716849</v>
@@ -2987,7 +2987,7 @@
         <v>338.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>104.8061665805111</v>
+        <v>385.4478973282775</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>60.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3039,7 +3039,7 @@
         <v>102.8896287080119</v>
       </c>
       <c r="G32" t="n">
-        <v>101.7573722870162</v>
+        <v>108.9819636724308</v>
       </c>
       <c r="H32" t="n">
         <v>106.0096587035274</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>7.224591385414723</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>192.8481678023229</v>
@@ -3221,19 +3221,19 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>303.7023614405202</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
         <v>385.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>423.839266425598</v>
+        <v>242.5660201821116</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>424.6021279811511</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>60.37347970285543</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>144.8481678023229</v>
@@ -3343,7 +3343,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3400,16 +3400,16 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V36" t="n">
-        <v>414.5106671915202</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>145.050905435271</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X36" t="n">
         <v>69.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>49.39139276613435</v>
+        <v>112.0691552915769</v>
       </c>
     </row>
     <row r="37">
@@ -3519,7 +3519,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>144.8481678023229</v>
@@ -3580,16 +3580,16 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>11.09991244551929</v>
+        <v>81.10557774904923</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3643,7 +3643,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X39" t="n">
-        <v>142.9042596329532</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y39" t="n">
         <v>49.39139276613435</v>
@@ -3814,16 +3814,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>34.55655664632661</v>
+        <v>99.29663227406654</v>
       </c>
       <c r="C42" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>267.2794625959092</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S42" t="n">
         <v>116.5639999646113</v>
@@ -3990,7 +3990,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H44" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>144.8481678023229</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>97.23431917176916</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>361.0999124455193</v>
+        <v>73.77767497096181</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -4321,19 +4321,19 @@
         <v>30.8</v>
       </c>
       <c r="J2" t="n">
-        <v>30.8</v>
+        <v>411.95</v>
       </c>
       <c r="K2" t="n">
-        <v>30.8</v>
+        <v>793.0999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>396.55</v>
+        <v>1158.85</v>
       </c>
       <c r="M2" t="n">
-        <v>777.6999999999999</v>
+        <v>1540</v>
       </c>
       <c r="N2" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="O2" t="n">
         <v>1540</v>
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>722.3619790837812</v>
+        <v>30.8</v>
       </c>
       <c r="C3" t="n">
-        <v>722.3619790837812</v>
+        <v>30.8</v>
       </c>
       <c r="D3" t="n">
-        <v>722.3619790837812</v>
+        <v>30.8</v>
       </c>
       <c r="E3" t="n">
-        <v>722.3619790837812</v>
+        <v>30.8</v>
       </c>
       <c r="F3" t="n">
-        <v>722.3619790837812</v>
+        <v>30.8</v>
       </c>
       <c r="G3" t="n">
-        <v>585.6429020987573</v>
+        <v>30.8</v>
       </c>
       <c r="H3" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="I3" t="n">
         <v>30.8</v>
@@ -4424,28 +4424,28 @@
         <v>1011.404879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>862.6434684666581</v>
+        <v>622.5159909842129</v>
       </c>
       <c r="S3" t="n">
-        <v>795.4071048660406</v>
+        <v>555.2796273835954</v>
       </c>
       <c r="T3" t="n">
-        <v>789.9952208079459</v>
+        <v>166.3907384947065</v>
       </c>
       <c r="U3" t="n">
-        <v>789.7827362016966</v>
+        <v>166.1782538884573</v>
       </c>
       <c r="V3" t="n">
-        <v>775.1254966143025</v>
+        <v>151.5210143010632</v>
       </c>
       <c r="W3" t="n">
-        <v>742.4253522609404</v>
+        <v>50.86337317715914</v>
       </c>
       <c r="X3" t="n">
-        <v>722.3619790837812</v>
+        <v>30.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>722.3619790837812</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="4">
@@ -4455,19 +4455,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>677.9023613151999</v>
+        <v>42.98476868153026</v>
       </c>
       <c r="C4" t="n">
-        <v>677.9023613151999</v>
+        <v>168.986774499966</v>
       </c>
       <c r="D4" t="n">
-        <v>677.9023613151999</v>
+        <v>282.3059186249661</v>
       </c>
       <c r="E4" t="n">
-        <v>677.9023613151999</v>
+        <v>400.1348228363792</v>
       </c>
       <c r="F4" t="n">
-        <v>677.9023613151999</v>
+        <v>524.4957954283146</v>
       </c>
       <c r="G4" t="n">
         <v>677.9023613151999</v>
@@ -4488,43 +4488,43 @@
         <v>1516.214517012344</v>
       </c>
       <c r="M4" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N4" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O4" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P4" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q4" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R4" t="n">
         <v>30.8</v>
       </c>
       <c r="S4" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T4" t="n">
-        <v>256.125934252978</v>
+        <v>30.8</v>
       </c>
       <c r="U4" t="n">
-        <v>502.6771268912646</v>
+        <v>30.8</v>
       </c>
       <c r="V4" t="n">
-        <v>677.9023613151999</v>
+        <v>42.98476868153026</v>
       </c>
       <c r="W4" t="n">
-        <v>677.9023613151999</v>
+        <v>42.98476868153026</v>
       </c>
       <c r="X4" t="n">
-        <v>677.9023613151999</v>
+        <v>42.98476868153026</v>
       </c>
       <c r="Y4" t="n">
-        <v>677.9023613151999</v>
+        <v>42.98476868153026</v>
       </c>
     </row>
     <row r="5">
@@ -4534,40 +4534,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C5" t="n">
-        <v>91.47201659665494</v>
+        <v>62.47586368209485</v>
       </c>
       <c r="D5" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E5" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F5" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G5" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H5" t="n">
-        <v>59.79615291456007</v>
+        <v>30.8</v>
       </c>
       <c r="I5" t="n">
         <v>30.8</v>
       </c>
       <c r="J5" t="n">
-        <v>30.8</v>
+        <v>396.55</v>
       </c>
       <c r="K5" t="n">
-        <v>411.9499999999999</v>
+        <v>396.55</v>
       </c>
       <c r="L5" t="n">
-        <v>793.0999999999999</v>
+        <v>396.55</v>
       </c>
       <c r="M5" t="n">
-        <v>1158.85</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="N5" t="n">
         <v>1158.85</v>
@@ -4585,25 +4585,25 @@
         <v>1540</v>
       </c>
       <c r="S5" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T5" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U5" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V5" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W5" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X5" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y5" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="6">
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.8</v>
+        <v>741.6808178458909</v>
       </c>
       <c r="C6" t="n">
-        <v>30.8</v>
+        <v>376.9334315372855</v>
       </c>
       <c r="D6" t="n">
-        <v>30.8</v>
+        <v>376.9334315372855</v>
       </c>
       <c r="E6" t="n">
         <v>30.8</v>
@@ -4658,31 +4658,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1011.404879873102</v>
+        <v>1186.232420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>862.6434684666581</v>
+        <v>1037.471008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>795.4071048660406</v>
+        <v>970.2346453614745</v>
       </c>
       <c r="T6" t="n">
-        <v>406.5182159771517</v>
+        <v>964.8227613033797</v>
       </c>
       <c r="U6" t="n">
-        <v>406.3057313709025</v>
+        <v>964.6102766971304</v>
       </c>
       <c r="V6" t="n">
-        <v>391.6484917835084</v>
+        <v>949.9530371097363</v>
       </c>
       <c r="W6" t="n">
-        <v>358.9483474301463</v>
+        <v>917.2528927563742</v>
       </c>
       <c r="X6" t="n">
-        <v>338.8849742529871</v>
+        <v>897.189519579215</v>
       </c>
       <c r="Y6" t="n">
-        <v>30.8</v>
+        <v>741.6808178458909</v>
       </c>
     </row>
     <row r="7">
@@ -4692,19 +4692,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>554.0138361142093</v>
+        <v>871.2301421292345</v>
       </c>
       <c r="C7" t="n">
-        <v>680.0158419326451</v>
+        <v>957.7833804114658</v>
       </c>
       <c r="D7" t="n">
-        <v>680.0158419326451</v>
+        <v>957.7833804114658</v>
       </c>
       <c r="E7" t="n">
-        <v>680.0158419326451</v>
+        <v>957.7833804114658</v>
       </c>
       <c r="F7" t="n">
-        <v>804.3768145245806</v>
+        <v>957.7833804114658</v>
       </c>
       <c r="G7" t="n">
         <v>957.7833804114658</v>
@@ -4749,19 +4749,19 @@
         <v>30.8</v>
       </c>
       <c r="U7" t="n">
-        <v>30.8</v>
+        <v>277.3511926382866</v>
       </c>
       <c r="V7" t="n">
-        <v>229.621392885946</v>
+        <v>476.1725855242326</v>
       </c>
       <c r="W7" t="n">
-        <v>330.8471977688849</v>
+        <v>648.0635037839101</v>
       </c>
       <c r="X7" t="n">
-        <v>330.8471977688849</v>
+        <v>648.0635037839101</v>
       </c>
       <c r="Y7" t="n">
-        <v>442.2564984479172</v>
+        <v>759.4728044629423</v>
       </c>
     </row>
     <row r="8">
@@ -4789,22 +4789,22 @@
         <v>67.88671726155745</v>
       </c>
       <c r="H8" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I8" t="n">
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
-        <v>411.9500000000024</v>
+        <v>30.8</v>
       </c>
       <c r="K8" t="n">
-        <v>793.1000000000024</v>
+        <v>411.9499999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>1158.849999999998</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>1540</v>
+        <v>1158.85</v>
       </c>
       <c r="N8" t="n">
         <v>1540</v>
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>482.234501601336</v>
+        <v>897.189519579215</v>
       </c>
       <c r="C9" t="n">
-        <v>482.234501601336</v>
+        <v>897.189519579215</v>
       </c>
       <c r="D9" t="n">
-        <v>482.234501601336</v>
+        <v>897.189519579215</v>
       </c>
       <c r="E9" t="n">
-        <v>482.234501601336</v>
+        <v>579.1494159256323</v>
       </c>
       <c r="F9" t="n">
-        <v>359.8298342171994</v>
+        <v>579.1494159256323</v>
       </c>
       <c r="G9" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="H9" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="I9" t="n">
         <v>30.8</v>
@@ -4895,31 +4895,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1011.404879873102</v>
+        <v>1186.232420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>622.5159909842129</v>
+        <v>1037.471008962092</v>
       </c>
       <c r="S9" t="n">
-        <v>555.2796273835954</v>
+        <v>970.2346453614745</v>
       </c>
       <c r="T9" t="n">
-        <v>549.8677433255007</v>
+        <v>964.8227613033797</v>
       </c>
       <c r="U9" t="n">
-        <v>549.6552587192514</v>
+        <v>964.6102766971304</v>
       </c>
       <c r="V9" t="n">
-        <v>534.9980191318573</v>
+        <v>949.9530371097363</v>
       </c>
       <c r="W9" t="n">
-        <v>502.2978747784952</v>
+        <v>917.2528927563742</v>
       </c>
       <c r="X9" t="n">
-        <v>482.234501601336</v>
+        <v>897.189519579215</v>
       </c>
       <c r="Y9" t="n">
-        <v>482.234501601336</v>
+        <v>897.189519579215</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.8188222554638</v>
+        <v>1075.695949146728</v>
       </c>
       <c r="C10" t="n">
-        <v>729.8208280738996</v>
+        <v>1103.757704828717</v>
       </c>
       <c r="D10" t="n">
-        <v>729.8208280738996</v>
+        <v>1217.076848953717</v>
       </c>
       <c r="E10" t="n">
-        <v>847.6497322853127</v>
+        <v>1217.076848953717</v>
       </c>
       <c r="F10" t="n">
-        <v>972.0107048772481</v>
+        <v>1217.076848953717</v>
       </c>
       <c r="G10" t="n">
-        <v>1125.417270764133</v>
+        <v>1370.483414840602</v>
       </c>
       <c r="H10" t="n">
-        <v>1294.933855923531</v>
+        <v>1540</v>
       </c>
       <c r="I10" t="n">
-        <v>1516.066734859614</v>
+        <v>1540</v>
       </c>
       <c r="J10" t="n">
-        <v>1516.066734859614</v>
+        <v>1540</v>
       </c>
       <c r="K10" t="n">
         <v>1540</v>
@@ -4980,25 +4980,25 @@
         <v>30.8</v>
       </c>
       <c r="S10" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T10" t="n">
-        <v>30.8</v>
+        <v>256.125934252978</v>
       </c>
       <c r="U10" t="n">
-        <v>30.8</v>
+        <v>502.6771268912646</v>
       </c>
       <c r="V10" t="n">
-        <v>229.621392885946</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="W10" t="n">
-        <v>229.621392885946</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="X10" t="n">
-        <v>380.6521839101395</v>
+        <v>852.529310801404</v>
       </c>
       <c r="Y10" t="n">
-        <v>492.0614845891717</v>
+        <v>963.9386114804363</v>
       </c>
     </row>
     <row r="11">
@@ -5008,49 +5008,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C11" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D11" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E11" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F11" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G11" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H11" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I11" t="n">
         <v>44.72</v>
       </c>
       <c r="J11" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K11" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="L11" t="n">
-        <v>436.0291130376557</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="M11" t="n">
-        <v>946.8779417665908</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N11" t="n">
-        <v>1500.287941766591</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="O11" t="n">
-        <v>1682.59</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P11" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>2236</v>
@@ -5059,25 +5059,25 @@
         <v>2236</v>
       </c>
       <c r="S11" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T11" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U11" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V11" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W11" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X11" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y11" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="12">
@@ -5269,22 +5269,22 @@
         <v>44.72</v>
       </c>
       <c r="J14" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183974</v>
       </c>
       <c r="K14" t="n">
-        <v>690.5809049473327</v>
+        <v>733.1420762183974</v>
       </c>
       <c r="L14" t="n">
-        <v>1243.990904947333</v>
+        <v>1286.552076218397</v>
       </c>
       <c r="M14" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="N14" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O14" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P14" t="n">
         <v>1797.400904947332</v>
@@ -5327,19 +5327,19 @@
         <v>472.7782575464261</v>
       </c>
       <c r="C15" t="n">
-        <v>396.1722089875784</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D15" t="n">
-        <v>44.72</v>
+        <v>110.1140157855959</v>
       </c>
       <c r="E15" t="n">
-        <v>44.72</v>
+        <v>110.1140157855959</v>
       </c>
       <c r="F15" t="n">
-        <v>44.72</v>
+        <v>110.1140157855959</v>
       </c>
       <c r="G15" t="n">
-        <v>44.72</v>
+        <v>110.1140157855959</v>
       </c>
       <c r="H15" t="n">
         <v>44.72</v>
@@ -5500,31 +5500,31 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H17" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I17" t="n">
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K17" t="n">
-        <v>733.1420762183976</v>
+        <v>598.13</v>
       </c>
       <c r="L17" t="n">
-        <v>733.1420762183976</v>
+        <v>1151.54</v>
       </c>
       <c r="M17" t="n">
-        <v>1243.990904947333</v>
+        <v>1151.54</v>
       </c>
       <c r="N17" t="n">
-        <v>1797.400904947332</v>
+        <v>1704.95</v>
       </c>
       <c r="O17" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P17" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q17" t="n">
         <v>2236</v>
@@ -5561,19 +5561,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C18" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D18" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E18" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F18" t="n">
-        <v>118.4993133207734</v>
+        <v>44.72</v>
       </c>
       <c r="G18" t="n">
         <v>44.72</v>
@@ -5618,19 +5618,19 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U18" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V18" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W18" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907175</v>
       </c>
       <c r="X18" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y18" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="19">
@@ -5731,34 +5731,34 @@
         <v>217.0655061454243</v>
       </c>
       <c r="F20" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G20" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H20" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I20" t="n">
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>44.72</v>
+        <v>137.1709049473328</v>
       </c>
       <c r="K20" t="n">
-        <v>598.13</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="L20" t="n">
-        <v>1151.54</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="M20" t="n">
         <v>1243.990904947333</v>
       </c>
       <c r="N20" t="n">
-        <v>1797.400904947332</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O20" t="n">
-        <v>1797.400904947332</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P20" t="n">
         <v>1797.400904947332</v>
@@ -5798,13 +5798,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C21" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D21" t="n">
-        <v>44.72</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="E21" t="n">
         <v>44.72</v>
@@ -5861,13 +5861,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W21" t="n">
-        <v>564.8317184882503</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X21" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y21" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="22">
@@ -5974,7 +5974,7 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H23" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I23" t="n">
         <v>44.72</v>
@@ -5983,22 +5983,22 @@
         <v>44.72</v>
       </c>
       <c r="K23" t="n">
-        <v>179.7320762183977</v>
+        <v>64.92117127106526</v>
       </c>
       <c r="L23" t="n">
-        <v>179.7320762183977</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="M23" t="n">
-        <v>690.5809049473327</v>
+        <v>1129.18</v>
       </c>
       <c r="N23" t="n">
-        <v>1243.990904947333</v>
+        <v>1682.59</v>
       </c>
       <c r="O23" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P23" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q23" t="n">
         <v>2236</v>
@@ -6038,13 +6038,13 @@
         <v>472.7782575464261</v>
       </c>
       <c r="C24" t="n">
-        <v>461.5662247731743</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="D24" t="n">
-        <v>461.5662247731743</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="E24" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F24" t="n">
         <v>44.72</v>
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C25" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D25" t="n">
         <v>1010.366979583462</v>
@@ -6168,22 +6168,22 @@
         <v>44.72</v>
       </c>
       <c r="T25" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U25" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V25" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W25" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X25" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y25" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="26">
@@ -6220,28 +6220,28 @@
         <v>449.9491130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>643.6617564436343</v>
+        <v>449.9491130376557</v>
       </c>
       <c r="L26" t="n">
-        <v>1369.331756443634</v>
+        <v>449.9491130376557</v>
       </c>
       <c r="M26" t="n">
-        <v>1880.180585172569</v>
+        <v>960.7979417665907</v>
       </c>
       <c r="N26" t="n">
-        <v>2493.400904947332</v>
+        <v>1574.018261541354</v>
       </c>
       <c r="O26" t="n">
-        <v>2493.400904947332</v>
+        <v>2206.33</v>
       </c>
       <c r="P26" t="n">
-        <v>2493.400904947332</v>
+        <v>2932</v>
       </c>
       <c r="Q26" t="n">
         <v>2932</v>
       </c>
       <c r="R26" t="n">
-        <v>2924.702432944026</v>
+        <v>2932</v>
       </c>
       <c r="S26" t="n">
         <v>2729.90630385077</v>
@@ -6299,7 +6299,7 @@
         <v>182.596520175299</v>
       </c>
       <c r="K27" t="n">
-        <v>619.744777677256</v>
+        <v>371.7893362696824</v>
       </c>
       <c r="L27" t="n">
         <v>891.0952392724561</v>
@@ -6381,19 +6381,19 @@
         <v>1182.871843630703</v>
       </c>
       <c r="L28" t="n">
-        <v>1182.871843630703</v>
+        <v>1061.749633009068</v>
       </c>
       <c r="M28" t="n">
-        <v>1182.871843630703</v>
+        <v>1061.749633009068</v>
       </c>
       <c r="N28" t="n">
-        <v>1182.871843630703</v>
+        <v>789.8455165730227</v>
       </c>
       <c r="O28" t="n">
-        <v>876.1017815695711</v>
+        <v>447.9813104326035</v>
       </c>
       <c r="P28" t="n">
-        <v>486.7604711369677</v>
+        <v>58.64</v>
       </c>
       <c r="Q28" t="n">
         <v>58.64</v>
@@ -6430,25 +6430,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>741.5271461350328</v>
+        <v>734.2295790790585</v>
       </c>
       <c r="C29" t="n">
-        <v>592.5629256875642</v>
+        <v>585.2653586315898</v>
       </c>
       <c r="D29" t="n">
-        <v>483.1294350412513</v>
+        <v>475.8318679852769</v>
       </c>
       <c r="E29" t="n">
-        <v>379.732172812091</v>
+        <v>372.4346057561166</v>
       </c>
       <c r="F29" t="n">
-        <v>275.8032549252104</v>
+        <v>268.505687869236</v>
       </c>
       <c r="G29" t="n">
-        <v>173.0180303928707</v>
+        <v>165.7204633368964</v>
       </c>
       <c r="H29" t="n">
-        <v>65.93756705597437</v>
+        <v>58.64</v>
       </c>
       <c r="I29" t="n">
         <v>58.64</v>
@@ -6457,22 +6457,22 @@
         <v>449.9491130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>449.9491130376557</v>
+        <v>1159.655479385524</v>
       </c>
       <c r="L29" t="n">
-        <v>449.9491130376557</v>
+        <v>1885.325479385524</v>
       </c>
       <c r="M29" t="n">
-        <v>960.7979417665907</v>
+        <v>2396.174308114459</v>
       </c>
       <c r="N29" t="n">
-        <v>1574.018261541354</v>
+        <v>2493.400904947332</v>
       </c>
       <c r="O29" t="n">
-        <v>2299.688261541354</v>
+        <v>2493.400904947332</v>
       </c>
       <c r="P29" t="n">
-        <v>2932</v>
+        <v>2493.400904947332</v>
       </c>
       <c r="Q29" t="n">
         <v>2932</v>
@@ -6481,25 +6481,25 @@
         <v>2932</v>
       </c>
       <c r="S29" t="n">
-        <v>2737.203870906745</v>
+        <v>2729.90630385077</v>
       </c>
       <c r="T29" t="n">
-        <v>2449.65277825163</v>
+        <v>2442.355211195655</v>
       </c>
       <c r="U29" t="n">
-        <v>2098.924195879295</v>
+        <v>2091.626628823321</v>
       </c>
       <c r="V29" t="n">
-        <v>1767.761545205736</v>
+        <v>1760.463978149762</v>
       </c>
       <c r="W29" t="n">
-        <v>1427.990357346193</v>
+        <v>1420.692790290219</v>
       </c>
       <c r="X29" t="n">
-        <v>1134.776384153599</v>
+        <v>1127.478817097625</v>
       </c>
       <c r="Y29" t="n">
-        <v>923.3446339689465</v>
+        <v>916.0470669129721</v>
       </c>
     </row>
     <row r="30">
@@ -6533,25 +6533,25 @@
         <v>142.664877967565</v>
       </c>
       <c r="J30" t="n">
-        <v>302.9204340224472</v>
+        <v>266.6213981428639</v>
       </c>
       <c r="K30" t="n">
-        <v>492.1132501168307</v>
+        <v>619.744777677256</v>
       </c>
       <c r="L30" t="n">
-        <v>763.4637117120308</v>
+        <v>891.0952392724561</v>
       </c>
       <c r="M30" t="n">
-        <v>849.5442534548901</v>
+        <v>977.1757810153154</v>
       </c>
       <c r="N30" t="n">
-        <v>982.8245380624584</v>
+        <v>1110.456065622884</v>
       </c>
       <c r="O30" t="n">
-        <v>1221.866989746177</v>
+        <v>1349.498517306602</v>
       </c>
       <c r="P30" t="n">
-        <v>1334.396334215684</v>
+        <v>1462.027861776109</v>
       </c>
       <c r="Q30" t="n">
         <v>1462.027861776109</v>
@@ -6618,25 +6618,25 @@
         <v>1182.871843630703</v>
       </c>
       <c r="L31" t="n">
-        <v>1060.096461653148</v>
+        <v>1182.871843630703</v>
       </c>
       <c r="M31" t="n">
-        <v>839.2564501354207</v>
+        <v>1061.749633009068</v>
       </c>
       <c r="N31" t="n">
-        <v>567.3523336993753</v>
+        <v>789.8455165730227</v>
       </c>
       <c r="O31" t="n">
-        <v>225.4881275589561</v>
+        <v>447.9813104326035</v>
       </c>
       <c r="P31" t="n">
-        <v>119.6233128311671</v>
+        <v>58.64</v>
       </c>
       <c r="Q31" t="n">
-        <v>119.6233128311671</v>
+        <v>58.64</v>
       </c>
       <c r="R31" t="n">
-        <v>119.6233128311671</v>
+        <v>58.64</v>
       </c>
       <c r="S31" t="n">
         <v>58.64</v>
@@ -6667,19 +6667,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>734.2295790790585</v>
+        <v>741.5271461350328</v>
       </c>
       <c r="C32" t="n">
-        <v>585.2653586315898</v>
+        <v>592.5629256875642</v>
       </c>
       <c r="D32" t="n">
-        <v>475.8318679852769</v>
+        <v>483.1294350412513</v>
       </c>
       <c r="E32" t="n">
-        <v>372.4346057561166</v>
+        <v>379.732172812091</v>
       </c>
       <c r="F32" t="n">
-        <v>268.505687869236</v>
+        <v>275.8032549252104</v>
       </c>
       <c r="G32" t="n">
         <v>165.7204633368964</v>
@@ -6691,10 +6691,10 @@
         <v>58.64</v>
       </c>
       <c r="J32" t="n">
-        <v>356.5908514963016</v>
+        <v>58.64</v>
       </c>
       <c r="K32" t="n">
-        <v>356.5908514963016</v>
+        <v>58.64</v>
       </c>
       <c r="L32" t="n">
         <v>356.5908514963016</v>
@@ -6715,28 +6715,28 @@
         <v>2932</v>
       </c>
       <c r="R32" t="n">
-        <v>2924.702432944026</v>
+        <v>2932</v>
       </c>
       <c r="S32" t="n">
-        <v>2729.90630385077</v>
+        <v>2737.203870906745</v>
       </c>
       <c r="T32" t="n">
-        <v>2442.355211195655</v>
+        <v>2449.65277825163</v>
       </c>
       <c r="U32" t="n">
-        <v>2091.626628823321</v>
+        <v>2098.924195879295</v>
       </c>
       <c r="V32" t="n">
-        <v>1760.463978149762</v>
+        <v>1767.761545205736</v>
       </c>
       <c r="W32" t="n">
-        <v>1420.692790290219</v>
+        <v>1427.990357346193</v>
       </c>
       <c r="X32" t="n">
-        <v>1127.478817097625</v>
+        <v>1134.776384153599</v>
       </c>
       <c r="Y32" t="n">
-        <v>916.0470669129721</v>
+        <v>923.3446339689465</v>
       </c>
     </row>
     <row r="33">
@@ -6785,7 +6785,7 @@
         <v>862.50062421531</v>
       </c>
       <c r="O33" t="n">
-        <v>1349.498517306602</v>
+        <v>1101.543075899029</v>
       </c>
       <c r="P33" t="n">
         <v>1462.027861776109</v>
@@ -6864,16 +6864,16 @@
         <v>1182.871843630703</v>
       </c>
       <c r="O34" t="n">
-        <v>876.1017815695711</v>
+        <v>1182.871843630703</v>
       </c>
       <c r="P34" t="n">
-        <v>486.7604711369677</v>
+        <v>793.5305331980992</v>
       </c>
       <c r="Q34" t="n">
-        <v>58.64</v>
+        <v>548.5143511959662</v>
       </c>
       <c r="R34" t="n">
-        <v>58.64</v>
+        <v>119.6233128311671</v>
       </c>
       <c r="S34" t="n">
         <v>58.64</v>
@@ -6904,25 +6904,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C35" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D35" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E35" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F35" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G35" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H35" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I35" t="n">
         <v>44.72</v>
@@ -6937,10 +6937,10 @@
         <v>1542.849113037656</v>
       </c>
       <c r="M35" t="n">
-        <v>1682.59</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="N35" t="n">
-        <v>2236</v>
+        <v>2096.259113037656</v>
       </c>
       <c r="O35" t="n">
         <v>2236</v>
@@ -6952,28 +6952,28 @@
         <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S35" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T35" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U35" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V35" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W35" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X35" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y35" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="36">
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>55.93203277325181</v>
+        <v>409.4673863086053</v>
       </c>
       <c r="C36" t="n">
         <v>44.72</v>
@@ -7043,16 +7043,16 @@
         <v>776.5100746769283</v>
       </c>
       <c r="V36" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W36" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X36" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y36" t="n">
-        <v>90.8376455473191</v>
+        <v>444.3729990826726</v>
       </c>
     </row>
     <row r="37">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C38" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D38" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E38" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F38" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G38" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H38" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I38" t="n">
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>64.92117127106526</v>
+        <v>179.7320762183974</v>
       </c>
       <c r="K38" t="n">
-        <v>64.92117127106526</v>
+        <v>733.1420762183974</v>
       </c>
       <c r="L38" t="n">
-        <v>618.3311712710653</v>
+        <v>1286.552076218397</v>
       </c>
       <c r="M38" t="n">
-        <v>1129.18</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="N38" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O38" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P38" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q38" t="n">
         <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S38" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T38" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U38" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V38" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W38" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X38" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y38" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="39">
@@ -7220,16 +7220,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>398.9989442256527</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C39" t="n">
-        <v>387.7869114524009</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="D39" t="n">
-        <v>387.7869114524009</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="E39" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F39" t="n">
         <v>44.72</v>
@@ -7286,10 +7286,10 @@
         <v>628.142589726071</v>
       </c>
       <c r="X39" t="n">
-        <v>483.794852723088</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y39" t="n">
-        <v>433.9045569997199</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="40">
@@ -7299,25 +7299,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C40" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D40" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E40" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F40" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G40" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H40" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I40" t="n">
         <v>1549.112886369176</v>
@@ -7353,22 +7353,22 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U40" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V40" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W40" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="41">
@@ -7414,7 +7414,7 @@
         <v>946.8779417665908</v>
       </c>
       <c r="N41" t="n">
-        <v>1500.287941766591</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="O41" t="n">
         <v>1500.287941766591</v>
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>402.0654643105373</v>
+        <v>407.3842417608302</v>
       </c>
       <c r="C42" t="n">
-        <v>390.8534315372855</v>
+        <v>396.1722089875784</v>
       </c>
       <c r="D42" t="n">
-        <v>390.8534315372855</v>
+        <v>44.72</v>
       </c>
       <c r="E42" t="n">
         <v>44.72</v>
@@ -7505,28 +7505,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>930.1731652211525</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S42" t="n">
-        <v>812.4317511154845</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T42" t="n">
-        <v>756.5148165523393</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U42" t="n">
-        <v>705.7972814410396</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V42" t="n">
-        <v>640.6349913485949</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W42" t="n">
-        <v>557.4297964901822</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X42" t="n">
-        <v>486.8613728079725</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y42" t="n">
-        <v>436.9710770846045</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="43">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C44" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D44" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E44" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F44" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G44" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H44" t="n">
         <v>44.72</v>
@@ -7639,16 +7639,16 @@
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>436.0291130376557</v>
+        <v>137.1709049473328</v>
       </c>
       <c r="K44" t="n">
-        <v>989.4391130376558</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="L44" t="n">
-        <v>1542.849113037656</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="M44" t="n">
-        <v>1797.400904947332</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N44" t="n">
         <v>1797.400904947332</v>
@@ -7663,28 +7663,28 @@
         <v>2236</v>
       </c>
       <c r="R44" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S44" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T44" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U44" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V44" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W44" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X44" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y44" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="45">
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>409.4673863086053</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C45" t="n">
         <v>44.72</v>
@@ -7964,22 +7964,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>35.04300624509033</v>
+        <v>420.0430062450903</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>384.9999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>369.4444444444445</v>
+        <v>369.4444444444443</v>
       </c>
       <c r="M2" t="n">
         <v>929.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>862.2489580698352</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>455.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P2" t="n">
         <v>0.2870600406814136</v>
@@ -8201,19 +8201,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>35.04300624509033</v>
+        <v>404.4874506895348</v>
       </c>
       <c r="K5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>913.7065720867616</v>
+        <v>929.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>477.2489580698352</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O5" t="n">
         <v>455.2478695740924</v>
@@ -8438,19 +8438,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>420.0430062450927</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K8" t="n">
-        <v>385.0000000000001</v>
+        <v>385</v>
       </c>
       <c r="L8" t="n">
-        <v>369.4444444444396</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="M8" t="n">
-        <v>929.2621276423197</v>
+        <v>929.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>477.2489580698352</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O8" t="n">
         <v>70.24786957409245</v>
@@ -8675,28 +8675,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>93.38475247205326</v>
       </c>
       <c r="M11" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N11" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O11" t="n">
-        <v>254.3913627391524</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P11" t="n">
         <v>559.2870600406815</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,16 +8912,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>171.4188408091281</v>
       </c>
       <c r="K14" t="n">
-        <v>257.1230221309868</v>
+        <v>559</v>
       </c>
       <c r="L14" t="n">
         <v>559</v>
       </c>
       <c r="M14" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
         <v>477.2489580698352</v>
@@ -8930,7 +8930,7 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P14" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9149,28 +9149,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
-        <v>300.1141042229715</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N17" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>606.6620109882336</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,25 +9386,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>35.04300624509033</v>
+        <v>128.4277587171436</v>
       </c>
       <c r="K20" t="n">
         <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>559.0000000000001</v>
+        <v>559</v>
       </c>
       <c r="M20" t="n">
-        <v>637.6468801143703</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N20" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O20" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9626,10 +9626,10 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K23" t="n">
-        <v>136.375834564038</v>
+        <v>20.40522350612653</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
@@ -9644,7 +9644,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,10 +9863,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>195.6693367737158</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>733</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9875,13 +9875,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>70.24786957409245</v>
+        <v>708.9465952898965</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>733.2870600406815</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,25 +10100,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>733</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>1096.663422488788</v>
+        <v>575.4576417394043</v>
       </c>
       <c r="O29" t="n">
-        <v>803.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
-        <v>638.9857857564858</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,13 +10334,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>336.0034623019607</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>300.9604560568704</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
@@ -10580,13 +10580,13 @@
         <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>685.4145387153924</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O35" t="n">
-        <v>70.24786957409245</v>
+        <v>211.4002806471673</v>
       </c>
       <c r="P35" t="n">
         <v>0.2870600406814136</v>
@@ -10808,10 +10808,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>55.44822975121687</v>
+        <v>171.4188408091281</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L38" t="n">
         <v>559</v>
@@ -10820,16 +10820,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O38" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11057,10 +11057,10 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P41" t="n">
         <v>300.4011642636528</v>
@@ -11282,7 +11282,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>128.4277587171436</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
@@ -11291,10 +11291,10 @@
         <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>801.3851497733039</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N44" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O44" t="n">
         <v>70.24786957409245</v>
@@ -22703,7 +22703,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5911706460559</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.591170646055787</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -24596,22 +24596,22 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>121.5476281577792</v>
+        <v>1.636639642360905</v>
       </c>
       <c r="M28" t="n">
         <v>218.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>269.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>34.74320263849478</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>423.839266425598</v>
       </c>
       <c r="R28" t="n">
         <v>424.6021279811511</v>
@@ -24833,10 +24833,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>121.5476281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>98.72062288713161</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -24845,7 +24845,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>280.6417307477664</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>423.839266425598</v>
@@ -24854,7 +24854,7 @@
         <v>424.6021279811511</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>60.37347970285543</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25079,19 +25079,19 @@
         <v>269.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>34.74320263849478</v>
+        <v>338.445564079015</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>181.2732462434864</v>
       </c>
       <c r="R34" t="n">
-        <v>424.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>60.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9789711.877922421</v>
+        <v>9789711.877922419</v>
       </c>
     </row>
     <row r="12">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13664553.4586438</v>
+        <v>13664553.45864379</v>
       </c>
     </row>
     <row r="16">
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1227855.380931163</v>
+        <v>1227855.380931162</v>
       </c>
       <c r="C2" t="n">
         <v>1227855.380931162</v>
@@ -26278,16 +26278,16 @@
         <v>1227855.380931162</v>
       </c>
       <c r="E2" t="n">
+        <v>1227892.614324279</v>
+      </c>
+      <c r="F2" t="n">
         <v>1227892.61432428</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1227892.614324279</v>
       </c>
-      <c r="G2" t="n">
-        <v>1227892.61432428</v>
-      </c>
       <c r="H2" t="n">
-        <v>1227892.61432428</v>
+        <v>1227892.614324279</v>
       </c>
       <c r="I2" t="n">
         <v>1227892.61432428</v>
@@ -26299,7 +26299,7 @@
         <v>1201472.069195665</v>
       </c>
       <c r="L2" t="n">
-        <v>1201472.069195665</v>
+        <v>1201472.069195664</v>
       </c>
       <c r="M2" t="n">
         <v>1227892.614324279</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.903039643</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128454</v>
+        <v>540947.4312259532</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>497080.9107622076</v>
+        <v>499048.754700107</v>
       </c>
       <c r="K4" t="n">
-        <v>495312.6122507454</v>
+        <v>497280.4561886448</v>
       </c>
       <c r="L4" t="n">
-        <v>493541.8013236981</v>
+        <v>495509.6452615976</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.6773203549</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626167</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116067</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>464385.6560316536</v>
+        <v>462869.8003433369</v>
       </c>
       <c r="C6" t="n">
-        <v>601963.6361654672</v>
+        <v>600447.7804771514</v>
       </c>
       <c r="D6" t="n">
-        <v>604024.4080777831</v>
+        <v>602508.5523894673</v>
       </c>
       <c r="E6" t="n">
-        <v>280139.2110977444</v>
+        <v>278397.3612846364</v>
       </c>
       <c r="F6" t="n">
-        <v>623330.1064432483</v>
+        <v>621588.2566301409</v>
       </c>
       <c r="G6" t="n">
-        <v>625275.6829114342</v>
+        <v>623533.8330983262</v>
       </c>
       <c r="H6" t="n">
-        <v>627223.9597287354</v>
+        <v>625482.1099156273</v>
       </c>
       <c r="I6" t="n">
-        <v>629174.9563720959</v>
+        <v>627433.1065589882</v>
       </c>
       <c r="J6" t="n">
-        <v>196067.9204334571</v>
+        <v>194100.0764955577</v>
       </c>
       <c r="K6" t="n">
-        <v>636204.2189449196</v>
+        <v>634236.3750070202</v>
       </c>
       <c r="L6" t="n">
-        <v>637975.0298719668</v>
+        <v>636007.1859340667</v>
       </c>
       <c r="M6" t="n">
-        <v>598606.5397821787</v>
+        <v>596864.6899690708</v>
       </c>
       <c r="N6" t="n">
-        <v>638971.4368170326</v>
+        <v>637229.587003925</v>
       </c>
       <c r="O6" t="n">
-        <v>399339.1760747705</v>
+        <v>397597.3262616631</v>
       </c>
       <c r="P6" t="n">
-        <v>642909.7789257804</v>
+        <v>641167.9291126727</v>
       </c>
     </row>
   </sheetData>
@@ -26987,10 +26987,10 @@
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
@@ -26999,16 +26999,16 @@
         <v>302</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>48</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>302</v>
@@ -27036,7 +27036,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -27045,22 +27045,22 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>-0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O3" t="n">
         <v>-0</v>
@@ -27094,7 +27094,7 @@
         <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>-0</v>
@@ -27527,13 +27527,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>190.3876496598537</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27560,13 +27560,13 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>162.2737972923793</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>20.35776521751382</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27575,7 +27575,7 @@
         <v>400</v>
       </c>
       <c r="W3" t="n">
-        <v>400</v>
+        <v>332.7220781971635</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27594,19 +27594,19 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -27642,16 +27642,16 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
-        <v>376.1654965030195</v>
+        <v>211.4781573692771</v>
       </c>
       <c r="W4" t="n">
         <v>226.3728098387097</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27721,7 +27721,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>371.2938086145853</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27752,13 +27752,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27803,7 +27803,7 @@
         <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>20.35776521751382</v>
+        <v>400</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27818,7 +27818,7 @@
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>94.3872682556771</v>
+        <v>245.4377780501435</v>
       </c>
     </row>
     <row r="7">
@@ -27831,7 +27831,7 @@
         <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>360.1527600644399</v>
       </c>
       <c r="D7" t="n">
         <v>285.5362180555555</v>
@@ -27840,10 +27840,10 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
         <v>228.7711261016186</v>
@@ -27885,13 +27885,13 @@
         <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
         <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>328.6210975992541</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
@@ -27925,10 +27925,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27995,10 +27995,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>27.81239460486574</v>
       </c>
       <c r="F9" t="n">
-        <v>218.4556216275816</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -28007,7 +28007,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,10 +28031,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>162.2737972923793</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28068,16 +28068,16 @@
         <v>400</v>
       </c>
       <c r="C10" t="n">
+        <v>301.0704544076289</v>
+      </c>
+      <c r="D10" t="n">
         <v>400</v>
       </c>
-      <c r="D10" t="n">
-        <v>285.5362180555555</v>
-      </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
         <v>400</v>
@@ -28086,13 +28086,13 @@
         <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J10" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>312.6957890944621</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,13 +28116,13 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
         <v>400</v>
@@ -28165,7 +28165,7 @@
         <v>350</v>
       </c>
       <c r="I11" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28195,7 +28195,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S11" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T11" t="n">
         <v>350</v>
@@ -28463,7 +28463,7 @@
         <v>350</v>
       </c>
       <c r="C15" t="n">
-        <v>285.2599243722601</v>
+        <v>350</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -28478,7 +28478,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H15" t="n">
-        <v>332.1680871864211</v>
+        <v>267.4280115586812</v>
       </c>
       <c r="I15" t="n">
         <v>217.1263858913485</v>
@@ -28636,10 +28636,10 @@
         <v>350</v>
       </c>
       <c r="H17" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28709,10 +28709,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
-        <v>252.6980156874617</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H18" t="n">
         <v>332.1680871864211</v>
@@ -28754,7 +28754,7 @@
         <v>350</v>
       </c>
       <c r="U18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>350</v>
@@ -28763,7 +28763,7 @@
         <v>350</v>
       </c>
       <c r="X18" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="Y18" t="n">
         <v>350</v>
@@ -28867,7 +28867,7 @@
         <v>350</v>
       </c>
       <c r="F20" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="G20" t="n">
         <v>350</v>
@@ -28876,7 +28876,7 @@
         <v>350</v>
       </c>
       <c r="I20" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28940,10 +28940,10 @@
         <v>350</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>277.9320215941727</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>339.6362423378769</v>
@@ -28997,10 +28997,10 @@
         <v>350</v>
       </c>
       <c r="W21" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Y21" t="n">
         <v>350</v>
@@ -29110,10 +29110,10 @@
         <v>350</v>
       </c>
       <c r="H23" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I23" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29174,16 +29174,16 @@
         <v>350</v>
       </c>
       <c r="C24" t="n">
-        <v>350</v>
+        <v>279.99433469647</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>269.6305770343469</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>325.7395358750273</v>
@@ -29256,55 +29256,55 @@
         <v>350</v>
       </c>
       <c r="D25" t="n">
+        <v>350</v>
+      </c>
+      <c r="E25" t="n">
+        <v>350</v>
+      </c>
+      <c r="F25" t="n">
+        <v>350</v>
+      </c>
+      <c r="G25" t="n">
+        <v>350</v>
+      </c>
+      <c r="H25" t="n">
+        <v>350</v>
+      </c>
+      <c r="I25" t="n">
+        <v>350</v>
+      </c>
+      <c r="J25" t="n">
+        <v>350</v>
+      </c>
+      <c r="K25" t="n">
+        <v>350</v>
+      </c>
+      <c r="L25" t="n">
+        <v>350</v>
+      </c>
+      <c r="M25" t="n">
+        <v>350</v>
+      </c>
+      <c r="N25" t="n">
+        <v>350</v>
+      </c>
+      <c r="O25" t="n">
+        <v>350</v>
+      </c>
+      <c r="P25" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>350</v>
+      </c>
+      <c r="R25" t="n">
+        <v>350</v>
+      </c>
+      <c r="S25" t="n">
+        <v>350</v>
+      </c>
+      <c r="T25" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="E25" t="n">
-        <v>350</v>
-      </c>
-      <c r="F25" t="n">
-        <v>350</v>
-      </c>
-      <c r="G25" t="n">
-        <v>350</v>
-      </c>
-      <c r="H25" t="n">
-        <v>350</v>
-      </c>
-      <c r="I25" t="n">
-        <v>350</v>
-      </c>
-      <c r="J25" t="n">
-        <v>350</v>
-      </c>
-      <c r="K25" t="n">
-        <v>350</v>
-      </c>
-      <c r="L25" t="n">
-        <v>350</v>
-      </c>
-      <c r="M25" t="n">
-        <v>350</v>
-      </c>
-      <c r="N25" t="n">
-        <v>350</v>
-      </c>
-      <c r="O25" t="n">
-        <v>350</v>
-      </c>
-      <c r="P25" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>350</v>
-      </c>
-      <c r="R25" t="n">
-        <v>350</v>
-      </c>
-      <c r="S25" t="n">
-        <v>350</v>
-      </c>
-      <c r="T25" t="n">
-        <v>350</v>
       </c>
       <c r="U25" t="n">
         <v>350</v>
@@ -29377,10 +29377,10 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>243.6540074428798</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S26" t="n">
-        <v>302</v>
+        <v>294.7754086145854</v>
       </c>
       <c r="T26" t="n">
         <v>302</v>
@@ -29435,10 +29435,10 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>250.460041825832</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>250.4600418258319</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -29587,7 +29587,7 @@
         <v>302</v>
       </c>
       <c r="I29" t="n">
-        <v>142.85656829727</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29617,7 +29617,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S29" t="n">
-        <v>302</v>
+        <v>294.7754086145854</v>
       </c>
       <c r="T29" t="n">
         <v>302</v>
@@ -29669,10 +29669,10 @@
         <v>302</v>
       </c>
       <c r="J30" t="n">
-        <v>36.66569280765994</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>165.5864277171806</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>302</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
         <v>302</v>
@@ -29818,7 +29818,7 @@
         <v>302</v>
       </c>
       <c r="G32" t="n">
-        <v>302</v>
+        <v>294.7754086145854</v>
       </c>
       <c r="H32" t="n">
         <v>302</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>243.6540074428798</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S32" t="n">
         <v>302</v>
@@ -29921,10 +29921,10 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>250.4600418258318</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>250.4600418258319</v>
       </c>
       <c r="Q33" t="n">
         <v>173.0792650904796</v>
@@ -30061,7 +30061,7 @@
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S35" t="n">
         <v>350</v>
@@ -30122,7 +30122,7 @@
         <v>350</v>
       </c>
       <c r="C36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
@@ -30179,16 +30179,16 @@
         <v>350</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="W36" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="X36" t="n">
         <v>350</v>
       </c>
       <c r="Y36" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
     </row>
     <row r="37">
@@ -30298,7 +30298,7 @@
         <v>350</v>
       </c>
       <c r="I38" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
         <v>350</v>
@@ -30359,16 +30359,16 @@
         <v>350</v>
       </c>
       <c r="C39" t="n">
-        <v>350</v>
+        <v>279.99433469647</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>325.7395358750273</v>
@@ -30422,7 +30422,7 @@
         <v>350</v>
       </c>
       <c r="X39" t="n">
-        <v>276.9584798124343</v>
+        <v>350</v>
       </c>
       <c r="Y39" t="n">
         <v>350</v>
@@ -30456,40 +30456,40 @@
         <v>350</v>
       </c>
       <c r="I40" t="n">
+        <v>350</v>
+      </c>
+      <c r="J40" t="n">
+        <v>350</v>
+      </c>
+      <c r="K40" t="n">
+        <v>350</v>
+      </c>
+      <c r="L40" t="n">
+        <v>350</v>
+      </c>
+      <c r="M40" t="n">
+        <v>350</v>
+      </c>
+      <c r="N40" t="n">
+        <v>350</v>
+      </c>
+      <c r="O40" t="n">
+        <v>350</v>
+      </c>
+      <c r="P40" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>350</v>
+      </c>
+      <c r="R40" t="n">
+        <v>350</v>
+      </c>
+      <c r="S40" t="n">
+        <v>350</v>
+      </c>
+      <c r="T40" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="J40" t="n">
-        <v>350</v>
-      </c>
-      <c r="K40" t="n">
-        <v>350</v>
-      </c>
-      <c r="L40" t="n">
-        <v>350</v>
-      </c>
-      <c r="M40" t="n">
-        <v>350</v>
-      </c>
-      <c r="N40" t="n">
-        <v>350</v>
-      </c>
-      <c r="O40" t="n">
-        <v>350</v>
-      </c>
-      <c r="P40" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>350</v>
-      </c>
-      <c r="R40" t="n">
-        <v>350</v>
-      </c>
-      <c r="S40" t="n">
-        <v>350</v>
-      </c>
-      <c r="T40" t="n">
-        <v>350</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30593,16 +30593,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>350</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="C42" t="n">
         <v>350</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
         <v>339.6362423378769</v>
@@ -30641,7 +30641,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>279.9943346964701</v>
+        <v>350</v>
       </c>
       <c r="S42" t="n">
         <v>350</v>
@@ -30769,7 +30769,7 @@
         <v>350</v>
       </c>
       <c r="H44" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I44" t="n">
         <v>150.0811596826846</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S44" t="n">
         <v>350</v>
@@ -30830,10 +30830,10 @@
         </is>
       </c>
       <c r="B45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" t="n">
         <v>287.3222374745575</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>347.9376868977026</v>
@@ -34743,22 +34743,22 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>384.9999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>369.4444444444445</v>
+        <v>369.4444444444443</v>
       </c>
       <c r="M2" t="n">
         <v>385</v>
       </c>
       <c r="N2" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -34880,19 +34880,19 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
         <v>171.2288738983814</v>
@@ -34928,16 +34928,16 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>176.9951862868033</v>
+        <v>12.30784715306086</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -34980,19 +34980,19 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>385</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>385</v>
-      </c>
-      <c r="M5" t="n">
-        <v>369.4444444444443</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>385</v>
@@ -35117,7 +35117,7 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>87.42751341639524</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -35171,13 +35171,13 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V7" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>102.2482877605444</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -35217,19 +35217,19 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>385.0000000000024</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>385.0000000000001</v>
+        <v>385</v>
       </c>
       <c r="L8" t="n">
-        <v>369.4444444444396</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="M8" t="n">
-        <v>385.0000000000024</v>
+        <v>385</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35354,16 +35354,16 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>28.34520775958426</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>154.95612715847</v>
@@ -35372,13 +35372,13 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>24.17501529331905</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,13 +35402,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
         <v>200.8296897837838</v>
@@ -35454,28 +35454,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>93.38475247205326</v>
       </c>
       <c r="M11" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>559</v>
-      </c>
-      <c r="O11" t="n">
-        <v>184.1434931650599</v>
       </c>
       <c r="P11" t="n">
         <v>559</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35691,16 +35691,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="K14" t="n">
-        <v>257.1230221309868</v>
+        <v>559</v>
       </c>
       <c r="L14" t="n">
         <v>559</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -35709,7 +35709,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>443.0293889420883</v>
@@ -35928,28 +35928,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>300.1141042229715</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>559</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>536.4141414141411</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36165,25 +36165,25 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>93.38475247205329</v>
       </c>
       <c r="K20" t="n">
         <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>559.0000000000001</v>
+        <v>559</v>
       </c>
       <c r="M20" t="n">
-        <v>93.38475247205298</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>559</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>443.0293889420883</v>
@@ -36405,10 +36405,10 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>136.375834564038</v>
+        <v>20.40522350612653</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
@@ -36423,7 +36423,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36542,7 +36542,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D25" t="n">
-        <v>56.67511257857869</v>
+        <v>64.46378194444452</v>
       </c>
       <c r="E25" t="n">
         <v>69.01909516304346</v>
@@ -36590,7 +36590,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U25" t="n">
         <v>199.0416087255421</v>
@@ -36642,10 +36642,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>195.6693367737158</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>733</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36654,13 +36654,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>638.698725715804</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>733</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36721,10 +36721,10 @@
         <v>125.2086062376757</v>
       </c>
       <c r="K27" t="n">
-        <v>441.5638964666233</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L27" t="n">
-        <v>274.091375348687</v>
+        <v>524.5514171745189</v>
       </c>
       <c r="M27" t="n">
         <v>86.95004216450428</v>
@@ -36879,25 +36879,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>733</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>619.4144644189528</v>
+        <v>98.20868366956907</v>
       </c>
       <c r="O29" t="n">
-        <v>733</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>638.6987257158042</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36955,10 +36955,10 @@
         <v>84.87361410865147</v>
       </c>
       <c r="J30" t="n">
-        <v>161.8742990453356</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K30" t="n">
-        <v>191.1038546407913</v>
+        <v>356.6902823579719</v>
       </c>
       <c r="L30" t="n">
         <v>274.091375348687</v>
@@ -36976,7 +36976,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q30" t="n">
-        <v>128.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37113,13 +37113,13 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>300.9604560568704</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>516.0089179080152</v>
@@ -37207,10 +37207,10 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O33" t="n">
-        <v>491.9170637285782</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>113.6660045146532</v>
+        <v>364.1260463404851</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -37359,13 +37359,13 @@
         <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>141.1524110730751</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>559</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>141.1524110730749</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -37587,10 +37587,10 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>20.40522350612654</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L38" t="n">
         <v>559</v>
@@ -37599,16 +37599,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37742,7 +37742,7 @@
         <v>121.2288738983814</v>
       </c>
       <c r="I40" t="n">
-        <v>165.577875014016</v>
+        <v>173.3665443798817</v>
       </c>
       <c r="J40" t="n">
         <v>314.7310511640923</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37836,10 +37836,10 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
         <v>559</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>300.1141042229714</v>
@@ -38061,7 +38061,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>395.2617303410664</v>
+        <v>93.38475247205329</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
@@ -38070,10 +38070,10 @@
         <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>257.1230221309866</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
